--- a/projetos/gestao-ia-planilhas/produto/kit-completo/01-semana-organizada.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/01-semana-organizada.xlsx
@@ -12058,22 +12058,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="D4:D303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4:D303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$B$9,0,0,MAX(1,COUNTA(Config!$B$9:$B$16)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:G303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4:G303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$D$9:$D$12</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:C303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C4:C303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$F$9,0,0,MAX(1,COUNTA(Config!$F$9:$F$16)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="E4:E303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="H4:H303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="H4:H303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/01-semana-organizada.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/01-semana-organizada.xlsx
@@ -945,7 +945,7 @@
     <row r="2">
       <c r="A2" s="7" t="str">
         <f>"Painel de "&amp;TEXT(Config!B4,"dd/mm/yyyy")&amp;". Nada para preencher aqui: tudo vem da aba Tarefas."</f>
-        <v>Painel de 17/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
+        <v>Painel de 18/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
       </c>
     </row>
     <row r="4">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C10" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46281.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D10" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C11" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C12" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46280.0</v>
+        <v>46281.0</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C13" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="D13" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C14" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="D14" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C15" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="D15" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C16" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="D16" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C17" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="D17" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C18" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="D18" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C19" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D19" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C20" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="D20" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C21" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="D21" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1450,11 +1450,11 @@
     <row r="25">
       <c r="A25" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B25),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qui</v>
+        <v>sex</v>
       </c>
       <c r="B25" s="25">
         <f>Config!$B$4+0</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="C25" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B25,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1478,11 +1478,11 @@
     <row r="26">
       <c r="A26" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B26),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sex</v>
+        <v>sáb</v>
       </c>
       <c r="B26" s="25">
         <f>Config!$B$4+1</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="C26" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B26,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1506,11 +1506,11 @@
     <row r="27">
       <c r="A27" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B27),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sáb</v>
+        <v>dom</v>
       </c>
       <c r="B27" s="25">
         <f>Config!$B$4+2</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="C27" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B27,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1534,11 +1534,11 @@
     <row r="28">
       <c r="A28" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B28),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>dom</v>
+        <v>seg</v>
       </c>
       <c r="B28" s="25">
         <f>Config!$B$4+3</f>
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="C28" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B28,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1562,11 +1562,11 @@
     <row r="29">
       <c r="A29" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B29),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>seg</v>
+        <v>ter</v>
       </c>
       <c r="B29" s="25">
         <f>Config!$B$4+4</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="C29" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B29,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1590,11 +1590,11 @@
     <row r="30">
       <c r="A30" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B30),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>ter</v>
+        <v>qua</v>
       </c>
       <c r="B30" s="25">
         <f>Config!$B$4+5</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="C30" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B30,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1618,11 +1618,11 @@
     <row r="31">
       <c r="A31" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B31),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qua</v>
+        <v>qui</v>
       </c>
       <c r="B31" s="25">
         <f>Config!$B$4+6</f>
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="C31" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B31,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B4" s="32">
         <f>TODAY()</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="E4" s="37">
         <f>TODAY()-1</f>
-        <v>46281.0</v>
+        <v>46282.0</v>
       </c>
       <c r="F4" s="38" t="n">
         <v>3</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E5" s="37">
         <f>TODAY()</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="F5" s="38" t="n">
         <v>3</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E6" s="37">
         <f>TODAY()-2</f>
-        <v>46280.0</v>
+        <v>46281.0</v>
       </c>
       <c r="F6" s="38" t="n">
         <v>1</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E7" s="37">
         <f>TODAY()+1</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>3</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E8" s="37">
         <f>TODAY()+1</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F8" s="38" t="n">
         <v>2</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E9" s="37">
         <f>TODAY()+1</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F9" s="38" t="n">
         <v>2</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="E10" s="37">
         <f>TODAY()+2</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="F10" s="38" t="n">
         <v>2</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="E11" s="37">
         <f>TODAY()+3</f>
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="F11" s="38" t="n">
         <v>3</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E12" s="37">
         <f>TODAY()+4</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F12" s="38" t="n">
         <v>2</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E13" s="37">
         <f>TODAY()+4</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F13" s="38" t="n">
         <v>3</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E14" s="37">
         <f>TODAY()+5</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F14" s="38" t="n">
         <v>1</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E15" s="37">
         <f>TODAY()+6</f>
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E16" s="37">
         <f>TODAY()+7</f>
-        <v>46289.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F16" s="38" t="n">
         <v>2</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E17" s="37">
         <f>TODAY()-9</f>
-        <v>46273.0</v>
+        <v>46274.0</v>
       </c>
       <c r="F17" s="38" t="n">
         <v>3</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E18" s="37">
         <f>TODAY()+10</f>
-        <v>46292.0</v>
+        <v>46293.0</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E19" s="37">
         <f>TODAY()+13</f>
-        <v>46295.0</v>
+        <v>46296.0</v>
       </c>
       <c r="F19" s="38" t="n">
         <v>2</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E20" s="37">
         <f>TODAY()+16</f>
-        <v>46298.0</v>
+        <v>46299.0</v>
       </c>
       <c r="F20" s="38" t="n">
         <v>3</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E21" s="37">
         <f>TODAY()-3</f>
-        <v>46279.0</v>
+        <v>46280.0</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>1</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E23" s="37">
         <f>TODAY()-6</f>
-        <v>46276.0</v>
+        <v>46277.0</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>2</v>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/01-semana-organizada.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/01-semana-organizada.xlsx
@@ -945,7 +945,7 @@
     <row r="2">
       <c r="A2" s="7" t="str">
         <f>"Painel de "&amp;TEXT(Config!B4,"dd/mm/yyyy")&amp;". Nada para preencher aqui: tudo vem da aba Tarefas."</f>
-        <v>Painel de 18/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
+        <v>Painel de 19/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
       </c>
     </row>
     <row r="4">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C10" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="D10" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C11" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C12" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46281.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C13" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="D13" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C14" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="D14" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C15" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="D15" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C16" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="D16" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C17" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="D17" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C18" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="D18" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C19" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46289.0</v>
+        <v>46290.0</v>
       </c>
       <c r="D19" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C20" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="D20" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C21" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D21" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1450,11 +1450,11 @@
     <row r="25">
       <c r="A25" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B25),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sex</v>
+        <v>sáb</v>
       </c>
       <c r="B25" s="25">
         <f>Config!$B$4+0</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="C25" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B25,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1478,11 +1478,11 @@
     <row r="26">
       <c r="A26" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B26),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sáb</v>
+        <v>dom</v>
       </c>
       <c r="B26" s="25">
         <f>Config!$B$4+1</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="C26" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B26,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1506,11 +1506,11 @@
     <row r="27">
       <c r="A27" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B27),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>dom</v>
+        <v>seg</v>
       </c>
       <c r="B27" s="25">
         <f>Config!$B$4+2</f>
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="C27" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B27,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1534,11 +1534,11 @@
     <row r="28">
       <c r="A28" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B28),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>seg</v>
+        <v>ter</v>
       </c>
       <c r="B28" s="25">
         <f>Config!$B$4+3</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="C28" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B28,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1562,11 +1562,11 @@
     <row r="29">
       <c r="A29" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B29),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>ter</v>
+        <v>qua</v>
       </c>
       <c r="B29" s="25">
         <f>Config!$B$4+4</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="C29" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B29,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1590,11 +1590,11 @@
     <row r="30">
       <c r="A30" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B30),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qua</v>
+        <v>qui</v>
       </c>
       <c r="B30" s="25">
         <f>Config!$B$4+5</f>
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="C30" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B30,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1618,11 +1618,11 @@
     <row r="31">
       <c r="A31" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B31),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qui</v>
+        <v>sex</v>
       </c>
       <c r="B31" s="25">
         <f>Config!$B$4+6</f>
-        <v>46289.0</v>
+        <v>46290.0</v>
       </c>
       <c r="C31" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B31,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B4" s="32">
         <f>TODAY()</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="E4" s="37">
         <f>TODAY()-1</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="F4" s="38" t="n">
         <v>3</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E5" s="37">
         <f>TODAY()</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F5" s="38" t="n">
         <v>3</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E6" s="37">
         <f>TODAY()-2</f>
-        <v>46281.0</v>
+        <v>46282.0</v>
       </c>
       <c r="F6" s="38" t="n">
         <v>1</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E7" s="37">
         <f>TODAY()+1</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>3</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E8" s="37">
         <f>TODAY()+1</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="F8" s="38" t="n">
         <v>2</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E9" s="37">
         <f>TODAY()+1</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="F9" s="38" t="n">
         <v>2</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="E10" s="37">
         <f>TODAY()+2</f>
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="F10" s="38" t="n">
         <v>2</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="E11" s="37">
         <f>TODAY()+3</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F11" s="38" t="n">
         <v>3</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E12" s="37">
         <f>TODAY()+4</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F12" s="38" t="n">
         <v>2</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E13" s="37">
         <f>TODAY()+4</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F13" s="38" t="n">
         <v>3</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E14" s="37">
         <f>TODAY()+5</f>
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="F14" s="38" t="n">
         <v>1</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E15" s="37">
         <f>TODAY()+6</f>
-        <v>46289.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E16" s="37">
         <f>TODAY()+7</f>
-        <v>46290.0</v>
+        <v>46291.0</v>
       </c>
       <c r="F16" s="38" t="n">
         <v>2</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E17" s="37">
         <f>TODAY()-9</f>
-        <v>46274.0</v>
+        <v>46275.0</v>
       </c>
       <c r="F17" s="38" t="n">
         <v>3</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E18" s="37">
         <f>TODAY()+10</f>
-        <v>46293.0</v>
+        <v>46294.0</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E19" s="37">
         <f>TODAY()+13</f>
-        <v>46296.0</v>
+        <v>46297.0</v>
       </c>
       <c r="F19" s="38" t="n">
         <v>2</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E20" s="37">
         <f>TODAY()+16</f>
-        <v>46299.0</v>
+        <v>46300.0</v>
       </c>
       <c r="F20" s="38" t="n">
         <v>3</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E21" s="37">
         <f>TODAY()-3</f>
-        <v>46280.0</v>
+        <v>46281.0</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>1</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E23" s="37">
         <f>TODAY()-6</f>
-        <v>46277.0</v>
+        <v>46278.0</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>2</v>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/01-semana-organizada.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/01-semana-organizada.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Faça upload do arquivo no Google Drive e abra com o Google Sheets. Tudo funciona: listas, cores e fórmulas.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Listas, cores e fórmulas funcionam.</t>
         </is>
       </c>
     </row>
@@ -944,8 +944,8 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="str">
-        <f>"Painel de "&amp;TEXT(Config!B4,"dd/mm/yyyy")&amp;". Nada para preencher aqui: tudo vem da aba Tarefas."</f>
-        <v>Painel de 19/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
+        <f>"Painel de "&amp;TEXT(DAY(Config!B4),"00")&amp;"/"&amp;TEXT(MONTH(Config!B4),"00")&amp;"/"&amp;YEAR(Config!B4)&amp;". Nada para preencher aqui: tudo vem da aba Tarefas."</f>
+        <v>Painel de 24/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
       </c>
     </row>
     <row r="4">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C10" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46283.0</v>
+        <v>46288.0</v>
       </c>
       <c r="D10" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C11" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46284.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C12" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46282.0</v>
+        <v>46287.0</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C13" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46285.0</v>
+        <v>46290.0</v>
       </c>
       <c r="D13" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C14" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46285.0</v>
+        <v>46290.0</v>
       </c>
       <c r="D14" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C15" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46287.0</v>
+        <v>46292.0</v>
       </c>
       <c r="D15" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C16" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46288.0</v>
+        <v>46293.0</v>
       </c>
       <c r="D16" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C17" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46285.0</v>
+        <v>46290.0</v>
       </c>
       <c r="D17" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C18" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46286.0</v>
+        <v>46291.0</v>
       </c>
       <c r="D18" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C19" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46290.0</v>
+        <v>46295.0</v>
       </c>
       <c r="D19" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C20" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46288.0</v>
+        <v>46293.0</v>
       </c>
       <c r="D20" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C21" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46289.0</v>
+        <v>46294.0</v>
       </c>
       <c r="D21" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1450,11 +1450,11 @@
     <row r="25">
       <c r="A25" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B25),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sáb</v>
+        <v>qui</v>
       </c>
       <c r="B25" s="25">
         <f>Config!$B$4+0</f>
-        <v>46284.0</v>
+        <v>46289.0</v>
       </c>
       <c r="C25" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B25,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1478,11 +1478,11 @@
     <row r="26">
       <c r="A26" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B26),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>dom</v>
+        <v>sex</v>
       </c>
       <c r="B26" s="25">
         <f>Config!$B$4+1</f>
-        <v>46285.0</v>
+        <v>46290.0</v>
       </c>
       <c r="C26" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B26,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1506,11 +1506,11 @@
     <row r="27">
       <c r="A27" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B27),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>seg</v>
+        <v>sáb</v>
       </c>
       <c r="B27" s="25">
         <f>Config!$B$4+2</f>
-        <v>46286.0</v>
+        <v>46291.0</v>
       </c>
       <c r="C27" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B27,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1534,11 +1534,11 @@
     <row r="28">
       <c r="A28" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B28),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>ter</v>
+        <v>dom</v>
       </c>
       <c r="B28" s="25">
         <f>Config!$B$4+3</f>
-        <v>46287.0</v>
+        <v>46292.0</v>
       </c>
       <c r="C28" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B28,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1562,11 +1562,11 @@
     <row r="29">
       <c r="A29" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B29),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qua</v>
+        <v>seg</v>
       </c>
       <c r="B29" s="25">
         <f>Config!$B$4+4</f>
-        <v>46288.0</v>
+        <v>46293.0</v>
       </c>
       <c r="C29" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B29,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1590,11 +1590,11 @@
     <row r="30">
       <c r="A30" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B30),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qui</v>
+        <v>ter</v>
       </c>
       <c r="B30" s="25">
         <f>Config!$B$4+5</f>
-        <v>46289.0</v>
+        <v>46294.0</v>
       </c>
       <c r="C30" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B30,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1618,11 +1618,11 @@
     <row r="31">
       <c r="A31" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B31),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sex</v>
+        <v>qua</v>
       </c>
       <c r="B31" s="25">
         <f>Config!$B$4+6</f>
-        <v>46290.0</v>
+        <v>46295.0</v>
       </c>
       <c r="C31" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B31,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B4" s="32">
         <f>TODAY()</f>
-        <v>46284.0</v>
+        <v>46289.0</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="E4" s="37">
         <f>TODAY()-1</f>
-        <v>46283.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F4" s="38" t="n">
         <v>3</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E5" s="37">
         <f>TODAY()</f>
-        <v>46284.0</v>
+        <v>46289.0</v>
       </c>
       <c r="F5" s="38" t="n">
         <v>3</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E6" s="37">
         <f>TODAY()-2</f>
-        <v>46282.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F6" s="38" t="n">
         <v>1</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E7" s="37">
         <f>TODAY()+1</f>
-        <v>46285.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>3</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E8" s="37">
         <f>TODAY()+1</f>
-        <v>46285.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F8" s="38" t="n">
         <v>2</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E9" s="37">
         <f>TODAY()+1</f>
-        <v>46285.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F9" s="38" t="n">
         <v>2</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="E10" s="37">
         <f>TODAY()+2</f>
-        <v>46286.0</v>
+        <v>46291.0</v>
       </c>
       <c r="F10" s="38" t="n">
         <v>2</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="E11" s="37">
         <f>TODAY()+3</f>
-        <v>46287.0</v>
+        <v>46292.0</v>
       </c>
       <c r="F11" s="38" t="n">
         <v>3</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E12" s="37">
         <f>TODAY()+4</f>
-        <v>46288.0</v>
+        <v>46293.0</v>
       </c>
       <c r="F12" s="38" t="n">
         <v>2</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E13" s="37">
         <f>TODAY()+4</f>
-        <v>46288.0</v>
+        <v>46293.0</v>
       </c>
       <c r="F13" s="38" t="n">
         <v>3</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E14" s="37">
         <f>TODAY()+5</f>
-        <v>46289.0</v>
+        <v>46294.0</v>
       </c>
       <c r="F14" s="38" t="n">
         <v>1</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E15" s="37">
         <f>TODAY()+6</f>
-        <v>46290.0</v>
+        <v>46295.0</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E16" s="37">
         <f>TODAY()+7</f>
-        <v>46291.0</v>
+        <v>46296.0</v>
       </c>
       <c r="F16" s="38" t="n">
         <v>2</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E17" s="37">
         <f>TODAY()-9</f>
-        <v>46275.0</v>
+        <v>46280.0</v>
       </c>
       <c r="F17" s="38" t="n">
         <v>3</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E18" s="37">
         <f>TODAY()+10</f>
-        <v>46294.0</v>
+        <v>46299.0</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E19" s="37">
         <f>TODAY()+13</f>
-        <v>46297.0</v>
+        <v>46302.0</v>
       </c>
       <c r="F19" s="38" t="n">
         <v>2</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E20" s="37">
         <f>TODAY()+16</f>
-        <v>46300.0</v>
+        <v>46305.0</v>
       </c>
       <c r="F20" s="38" t="n">
         <v>3</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E21" s="37">
         <f>TODAY()-3</f>
-        <v>46281.0</v>
+        <v>46286.0</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>1</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E23" s="37">
         <f>TODAY()-6</f>
-        <v>46278.0</v>
+        <v>46283.0</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>2</v>
